--- a/Farol_Intensidade_CLEAR_2026.xlsx
+++ b/Farol_Intensidade_CLEAR_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caiod\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B738BBB-3F42-484A-85FD-A0A20FAC41FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA1E264-13AD-4877-BA84-FF6324612694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,10 +170,10 @@
     <t>← Luan, preencha aqui →</t>
   </si>
   <si>
-    <t>Luiggi</t>
-  </si>
-  <si>
-    <t>← Luiggi, preencha aqui →</t>
+    <t>Luigi</t>
+  </si>
+  <si>
+    <t>← Luigi, preencha aqui →</t>
   </si>
   <si>
     <t>Lycia</t>
@@ -892,7 +892,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="9">
         <v>1</v>
@@ -904,16 +904,16 @@
         <v>1</v>
       </c>
       <c r="G5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="9">
         <v>1</v>
       </c>
       <c r="J5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="9">
         <v>1</v>
@@ -922,10 +922,10 @@
         <v>1</v>
       </c>
       <c r="M5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -942,34 +942,34 @@
         <v>1</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="9">
         <v>1</v>
       </c>
       <c r="G6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
       </c>
       <c r="K6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -980,40 +980,40 @@
         <v>26</v>
       </c>
       <c r="C7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1024,7 +1024,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="9">
         <v>1</v>
@@ -1036,16 +1036,16 @@
         <v>1</v>
       </c>
       <c r="G8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="9">
         <v>1</v>
       </c>
       <c r="J8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="9">
         <v>1</v>
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1074,34 +1074,34 @@
         <v>1</v>
       </c>
       <c r="E9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
       </c>
       <c r="G9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="9">
         <v>1</v>
       </c>
       <c r="K9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,40 +1112,40 @@
         <v>32</v>
       </c>
       <c r="C10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1156,7 +1156,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -1168,16 +1168,16 @@
         <v>1</v>
       </c>
       <c r="G11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="9">
         <v>1</v>
       </c>
       <c r="J11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="9">
         <v>1</v>
@@ -1186,10 +1186,10 @@
         <v>1</v>
       </c>
       <c r="M11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1206,34 +1206,34 @@
         <v>1</v>
       </c>
       <c r="E12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="9">
         <v>1</v>
       </c>
       <c r="G12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
       </c>
       <c r="K12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1244,40 +1244,40 @@
         <v>38</v>
       </c>
       <c r="C13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1288,7 +1288,7 @@
         <v>40</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="9">
         <v>1</v>
@@ -1300,16 +1300,16 @@
         <v>1</v>
       </c>
       <c r="G14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="9">
         <v>1</v>
       </c>
       <c r="J14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="9">
         <v>1</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="M14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1338,34 +1338,34 @@
         <v>1</v>
       </c>
       <c r="E15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="9">
         <v>1</v>
       </c>
       <c r="G15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="9">
         <v>1</v>
       </c>
       <c r="K15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1376,40 +1376,40 @@
         <v>44</v>
       </c>
       <c r="C16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K16" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1420,7 +1420,7 @@
         <v>46</v>
       </c>
       <c r="C17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
@@ -1432,16 +1432,16 @@
         <v>1</v>
       </c>
       <c r="G17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="9">
         <v>1</v>
       </c>
       <c r="J17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="9">
         <v>1</v>
@@ -1450,10 +1450,10 @@
         <v>1</v>
       </c>
       <c r="M17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1470,34 +1470,34 @@
         <v>1</v>
       </c>
       <c r="E18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="9">
         <v>1</v>
       </c>
       <c r="G18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
       </c>
       <c r="K18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1508,40 +1508,40 @@
         <v>50</v>
       </c>
       <c r="C19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1555,37 +1555,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1597,51 +1597,51 @@
       </c>
       <c r="C21" s="5">
         <f t="shared" ref="C21:N21" si="0">SUM(C5:C20)</f>
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="M21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="N21" s="5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Farol_Intensidade_CLEAR_2026.xlsx
+++ b/Farol_Intensidade_CLEAR_2026.xlsx
@@ -5,18 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caiod\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fgvbr.sharepoint.com/sites/ClearLAB2/Documentos Compartilhados/General/00. Cronogramas e Senhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA1E264-13AD-4877-BA84-FF6324612694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{FF935CB5-57A1-41DE-909F-D93E14AD978D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07DFB563-2A83-4EB1-8211-6533FC4DCFFF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1905" yWindow="-13620" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farol de Intensidade" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -775,14 +778,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="14" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -802,7 +805,7 @@
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
     </row>
-    <row r="2" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -822,7 +825,7 @@
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
     </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
@@ -840,7 +843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -884,7 +887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
@@ -892,43 +895,43 @@
         <v>22</v>
       </c>
       <c r="C5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="9">
         <v>3</v>
       </c>
       <c r="I5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>23</v>
       </c>
@@ -936,43 +939,43 @@
         <v>24</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>25</v>
       </c>
@@ -980,43 +983,43 @@
         <v>26</v>
       </c>
       <c r="C7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
@@ -1024,43 +1027,43 @@
         <v>28</v>
       </c>
       <c r="C8" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
@@ -1068,43 +1071,43 @@
         <v>30</v>
       </c>
       <c r="C9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>31</v>
       </c>
@@ -1112,43 +1115,43 @@
         <v>32</v>
       </c>
       <c r="C10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>33</v>
       </c>
@@ -1156,43 +1159,43 @@
         <v>34</v>
       </c>
       <c r="C11" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>35</v>
       </c>
@@ -1200,43 +1203,43 @@
         <v>36</v>
       </c>
       <c r="C12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>37</v>
       </c>
@@ -1244,43 +1247,43 @@
         <v>38</v>
       </c>
       <c r="C13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>39</v>
       </c>
@@ -1288,43 +1291,43 @@
         <v>40</v>
       </c>
       <c r="C14" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>41</v>
       </c>
@@ -1332,43 +1335,43 @@
         <v>42</v>
       </c>
       <c r="C15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>43</v>
       </c>
@@ -1376,43 +1379,43 @@
         <v>44</v>
       </c>
       <c r="C16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>45</v>
       </c>
@@ -1420,43 +1423,43 @@
         <v>46</v>
       </c>
       <c r="C17" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>47</v>
       </c>
@@ -1464,43 +1467,43 @@
         <v>48</v>
       </c>
       <c r="C18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>49</v>
       </c>
@@ -1508,43 +1511,43 @@
         <v>50</v>
       </c>
       <c r="C19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>51</v>
       </c>
@@ -1552,19 +1555,19 @@
         <v>52</v>
       </c>
       <c r="C20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="9">
         <v>2</v>
@@ -1573,22 +1576,22 @@
         <v>2</v>
       </c>
       <c r="J20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>53</v>
       </c>
@@ -1597,54 +1600,54 @@
       </c>
       <c r="C21" s="5">
         <f t="shared" ref="C21:N21" si="0">SUM(C5:C20)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="J21" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K21" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M21" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N21" s="5">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>55</v>
       </c>
@@ -1687,4 +1690,364 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="53b384bf-b751-4e05-97c8-c72dd0c21351" xsi:nil="true"/>
+    <Data xmlns="3ea11658-226e-40d5-a290-01cb485fca17" xsi:nil="true"/>
+    <xb1l xmlns="3ea11658-226e-40d5-a290-01cb485fca17" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ea11658-226e-40d5-a290-01cb485fca17">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <EMAILTESTE xmlns="3ea11658-226e-40d5-a290-01cb485fca17" xsi:nil="true"/>
+    <E_x002d_mailparacontato xmlns="3ea11658-226e-40d5-a290-01cb485fca17" xsi:nil="true"/>
+    <Nomecompleto xmlns="3ea11658-226e-40d5-a290-01cb485fca17" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010004CFED403076D64EB9A4D1FEC9D94FDA" ma:contentTypeVersion="24" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="15e776f1d78ea301efbd46e920417704">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ea11658-226e-40d5-a290-01cb485fca17" xmlns:ns3="53b384bf-b751-4e05-97c8-c72dd0c21351" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d4e54741e09f20093404976b7626e9c5" ns2:_="" ns3:_="">
+    <xsd:import namespace="3ea11658-226e-40d5-a290-01cb485fca17"/>
+    <xsd:import namespace="53b384bf-b751-4e05-97c8-c72dd0c21351"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:xb1l" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:Nomecompleto" minOccurs="0"/>
+                <xsd:element ref="ns2:E_x002d_mailparacontato" minOccurs="0"/>
+                <xsd:element ref="ns2:EMAILTESTE" minOccurs="0"/>
+                <xsd:element ref="ns2:Data" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3ea11658-226e-40d5-a290-01cb485fca17" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="xb1l" ma:index="20" nillable="true" ma:displayName="Data e hora" ma:internalName="xb1l">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="df19fe77-5e58-4a19-b499-fd74128cddae" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Nomecompleto" ma:index="27" nillable="true" ma:displayName="Nome completo" ma:format="Dropdown" ma:internalName="Nomecompleto">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="E_x002d_mailparacontato" ma:index="28" nillable="true" ma:displayName="E-mail para contato" ma:format="Dropdown" ma:internalName="E_x002d_mailparacontato">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="EMAILTESTE" ma:index="29" nillable="true" ma:displayName="E-mail teste" ma:format="Dropdown" ma:internalName="EMAILTESTE">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Data" ma:index="30" nillable="true" ma:displayName="Data" ma:format="DateTime" ma:internalName="Data">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="31" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="53b384bf-b751-4e05-97c8-c72dd0c21351" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5d86c675-f181-47ab-838d-71ac082c8817}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="53b384bf-b751-4e05-97c8-c72dd0c21351">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829F2BFC-9BE0-447F-9D7F-B60B36C73030}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007E9655-63D5-4429-A7D7-AB6CE07193EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="53b384bf-b751-4e05-97c8-c72dd0c21351"/>
+    <ds:schemaRef ds:uri="3ea11658-226e-40d5-a290-01cb485fca17"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D119EDF-1893-4C3D-8143-5C3F29FB0655}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ea11658-226e-40d5-a290-01cb485fca17"/>
+    <ds:schemaRef ds:uri="53b384bf-b751-4e05-97c8-c72dd0c21351"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>